--- a/data/semanas/321_pe.xlsx
+++ b/data/semanas/321_pe.xlsx
@@ -2924,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="b">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="b">
         <v>0</v>
@@ -4308,7 +4308,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W28" t="b">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="V32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W32" t="b">
         <v>0</v>
